--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_142_R15.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_142_R15.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6797</v>
+        <v>6.6533</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3326</v>
+        <v>5.184</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3471</v>
+        <v>1.4693</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8986</v>
+        <v>4.0143</v>
       </c>
       <c r="H2" t="n">
-        <v>2.497</v>
+        <v>3.7164</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4016</v>
+        <v>0.2978</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1813</v>
+        <v>4.9613</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9865</v>
+        <v>3.5528</v>
       </c>
       <c r="L2" t="n">
-        <v>2.1949</v>
+        <v>1.4085</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2828</v>
+        <v>-0.9471000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5105</v>
+        <v>0.1636</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.7933</v>
+        <v>-1.1107</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9278</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0647</v>
+        <v>-0.1858</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7027</v>
+        <v>-0.0507</v>
       </c>
       <c r="U2" t="n">
-        <v>0.362</v>
+        <v>-0.1351</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7886</v>
+        <v>3.7527</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6083</v>
+        <v>3.7527</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3565</v>
+        <v>5.8376</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1225</v>
+        <v>5.6249</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2341</v>
+        <v>0.2127</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0143</v>
+        <v>2.8986</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7164</v>
+        <v>2.497</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2978</v>
+        <v>0.4016</v>
       </c>
       <c r="J3" t="n">
-        <v>4.9613</v>
+        <v>4.1813</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5528</v>
+        <v>1.9865</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4085</v>
+        <v>2.1949</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-1.2828</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1636</v>
+        <v>0.5105</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1107</v>
+        <v>-1.7933</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9278</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4826</v>
+        <v>1.2226</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1123</v>
+        <v>0.995</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3703</v>
+        <v>0.2276</v>
       </c>
       <c r="V3" t="n">
-        <v>3.7527</v>
+        <v>0.7886</v>
       </c>
       <c r="W3" t="n">
-        <v>3.7527</v>
+        <v>1.6083</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. KONDIC</t>
+          <t>T. ARMSTRONG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2771</v>
+        <v>0.3283</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6923</v>
+        <v>0.2005</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4152</v>
+        <v>0.1278</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.2804</v>
+        <v>-0.1788</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9351</v>
+        <v>-0.3361</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.2155</v>
+        <v>0.1573</v>
       </c>
       <c r="J4" t="n">
-        <v>0.946</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0537</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1077</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2264</v>
+        <v>-0.1788</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1186</v>
+        <v>-0.3361</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.1078</v>
+        <v>0.1573</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5395</v>
+        <v>0.2752</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8338</v>
+        <v>0.2005</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2943</v>
+        <v>0.0747</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. ARMSTRONG</t>
+          <t>K. KONDIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2104</v>
+        <v>0.1248</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08260000000000001</v>
+        <v>1.3384</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1278</v>
+        <v>-1.2136</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1788</v>
+        <v>-1.2804</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3361</v>
+        <v>1.9351</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1573</v>
+        <v>-3.2155</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.946</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2.0537</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.1077</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1788</v>
+        <v>-2.2264</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3361</v>
+        <v>-0.1186</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1573</v>
+        <v>-2.1078</v>
       </c>
       <c r="P5" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1573</v>
+        <v>0.3872</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.4799</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0747</v>
+        <v>-0.0927</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>D. BERTANS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1311</v>
+        <v>-0.583</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5119</v>
+        <v>-3.1946</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3808</v>
+        <v>2.6116</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5753</v>
+        <v>-3.5294</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0574</v>
+        <v>0.0409</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6327</v>
+        <v>-3.5703</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8507</v>
+        <v>-3.6184</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8507</v>
+        <v>0.474</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-4.0924</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.426</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2067</v>
+        <v>-0.4331</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6327</v>
+        <v>0.5221</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2399</v>
+        <v>0.4826</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9085</v>
+        <v>0.5113</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6686</v>
+        <v>-0.0288</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9304</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
         <v>1.0722</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9993</v>
+        <v>-0.6962</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0655</v>
+        <v>0.1704</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9339</v>
+        <v>-0.8667</v>
       </c>
       <c r="G7" t="n">
         <v>-3.3559</v>
@@ -1000,13 +1000,13 @@
         <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1942</v>
+        <v>0.4973</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1098</v>
+        <v>0.1261</v>
       </c>
       <c r="U7" t="n">
-        <v>0.304</v>
+        <v>0.3712</v>
       </c>
       <c r="V7" t="n">
         <v>1.4665</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ANDERSON</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2166</v>
+        <v>-0.8125</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5809</v>
+        <v>-0.4317</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3643</v>
+        <v>-0.3808</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6559</v>
+        <v>-0.5753</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1177</v>
+        <v>1.0574</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4618</v>
+        <v>-1.6327</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1035</v>
+        <v>0.8507</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0334</v>
+        <v>0.8507</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0701</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4476</v>
+        <v>-1.426</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9157</v>
+        <v>0.2067</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5319</v>
+        <v>-1.6327</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8439</v>
+        <v>-0.7038</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0474</v>
+        <v>-0.0351</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7965</v>
+        <v>-0.6686</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.3247</v>
+        <v>0.9304</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.2525</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. KAMENJAS</t>
+          <t>J. ANDERSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4494</v>
+        <v>-0.9293</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2113</v>
+        <v>-0.9911</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.238</v>
+        <v>0.0618</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7101</v>
+        <v>0.6559</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3254</v>
+        <v>1.1177</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3848</v>
+        <v>-0.4618</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9308999999999999</v>
+        <v>2.1035</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9677</v>
+        <v>2.0334</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0368</v>
+        <v>0.0701</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7792</v>
+        <v>-1.4476</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3577</v>
+        <v>-0.9157</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4216</v>
+        <v>-0.5319</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6959</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7789</v>
+        <v>1.1312</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7196</v>
+        <v>0.6372</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0593</v>
+        <v>0.494</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.214</v>
+        <v>-1.3247</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.2525</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BERTANS</t>
+          <t>K. KAMENJAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.493</v>
+        <v>-1.4665</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1382</v>
+        <v>-0.3293</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6452</v>
+        <v>-1.1372</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.5294</v>
+        <v>-1.7101</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0409</v>
+        <v>-1.3254</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.5703</v>
+        <v>-0.3848</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.6184</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.474</v>
+        <v>-0.9677</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.0924</v>
+        <v>0.0368</v>
       </c>
       <c r="M10" t="n">
-        <v>0.08890000000000001</v>
+        <v>-0.7792</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4331</v>
+        <v>-0.3577</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5221</v>
+        <v>-0.4216</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5515</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4274</v>
+        <v>0.7617</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4323</v>
+        <v>0.6016</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0048</v>
+        <v>0.1601</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.567</v>
+        <v>-2.5271</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3408</v>
+        <v>-2.1665</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2262</v>
+        <v>-0.3606</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8849</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3179</v>
+        <v>0.3578</v>
       </c>
       <c r="T11" t="n">
-        <v>1.274</v>
+        <v>0.4483</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0439</v>
+        <v>-0.0905</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.929500000000001</v>
+        <v>5.929399999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>5.4052</v>
+        <v>5.405000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5244000000000002</v>
+        <v>0.5243</v>
       </c>
       <c r="G12" t="n">
         <v>-5.946</v>
@@ -1363,13 +1363,13 @@
         <v>-11.8279</v>
       </c>
       <c r="J12" t="n">
-        <v>6.098100000000001</v>
+        <v>6.0981</v>
       </c>
       <c r="K12" t="n">
         <v>8.4246</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.3264</v>
+        <v>-2.326399999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-12.0445</v>
@@ -1390,13 +1390,13 @@
         <v>17.3966</v>
       </c>
       <c r="S12" t="n">
-        <v>4.2263</v>
+        <v>4.226</v>
       </c>
       <c r="T12" t="n">
-        <v>3.9142</v>
+        <v>3.9141</v>
       </c>
       <c r="U12" t="n">
-        <v>0.312</v>
+        <v>0.3119</v>
       </c>
       <c r="V12" t="n">
         <v>5.3299</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.9987</v>
+        <v>4.9365</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0447</v>
+        <v>2.6909</v>
       </c>
       <c r="F13" t="n">
-        <v>1.954</v>
+        <v>2.2457</v>
       </c>
       <c r="G13" t="n">
         <v>2.0243</v>
@@ -1468,13 +1468,13 @@
         <v>2.5515</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5105</v>
+        <v>0.4483</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6176</v>
+        <v>0.2638</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1072</v>
+        <v>0.1845</v>
       </c>
       <c r="V13" t="n">
         <v>1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.906</v>
+        <v>1.5928</v>
       </c>
       <c r="E14" t="n">
         <v>-0.3333</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2394</v>
+        <v>1.9261</v>
       </c>
       <c r="G14" t="n">
         <v>1.2614</v>
@@ -1546,13 +1546,13 @@
         <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8224</v>
+        <v>0.5091</v>
       </c>
       <c r="T14" t="n">
         <v>0.0553</v>
       </c>
       <c r="U14" t="n">
-        <v>0.767</v>
+        <v>0.4538</v>
       </c>
       <c r="V14" t="n">
         <v>1.214</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>X. RATHAN-MAYES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2101</v>
+        <v>1.2022</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.6773</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2429</v>
+        <v>0.5249</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.2045</v>
+        <v>1.1088</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.814</v>
+        <v>0.7575</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6095</v>
+        <v>0.3513</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9574</v>
+        <v>0.8266</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.7303</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7729</v>
+        <v>0.0368</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2472</v>
+        <v>0.2822</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0838</v>
+        <v>-0.0323</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8366</v>
+        <v>0.3145</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>1.791</v>
+        <v>-0.1386</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4065</v>
+        <v>-0.1494</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6155</v>
+        <v>0.0108</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X. RATHAN-MAYES</t>
+          <t>J. JESSUP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1014</v>
+        <v>1.1417</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6773</v>
+        <v>-0.3716</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4241</v>
+        <v>1.5133</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1088</v>
+        <v>-0.6107</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7575</v>
+        <v>-0.0888</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3513</v>
+        <v>-0.5219</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8266</v>
+        <v>-0.5212</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.1547</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0368</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2822</v>
+        <v>-0.0895</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0323</v>
+        <v>-0.2435</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3145</v>
+        <v>0.154</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2394</v>
+        <v>-0.1032</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1494</v>
+        <v>0.1496</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0901</v>
+        <v>-0.2528</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. JESSUP</t>
+          <t>S. DINWIDDIE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4282</v>
+        <v>0.4457</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9614</v>
+        <v>2.4158</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3896</v>
+        <v>-1.9701</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6107</v>
+        <v>2.12</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0888</v>
+        <v>-1.9386</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5219</v>
+        <v>4.0586</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5212</v>
+        <v>3.6398</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1547</v>
+        <v>-0.1611</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6758999999999999</v>
+        <v>3.8008</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0895</v>
+        <v>-1.5198</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2435</v>
+        <v>-1.7775</v>
       </c>
       <c r="O17" t="n">
-        <v>0.154</v>
+        <v>0.2578</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8556</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8167</v>
+        <v>-0.9425</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4402</v>
+        <v>-0.1727</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3765</v>
+        <v>-0.7699</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.3558</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.428</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. DINWIDDIE</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2956</v>
+        <v>-0.1159</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7081</v>
+        <v>-0.6841</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0037</v>
+        <v>0.5682</v>
       </c>
       <c r="G18" t="n">
-        <v>2.12</v>
+        <v>-1.2045</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.9386</v>
+        <v>-2.814</v>
       </c>
       <c r="I18" t="n">
-        <v>4.0586</v>
+        <v>1.6095</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6398</v>
+        <v>-0.9574</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1611</v>
+        <v>-1.7303</v>
       </c>
       <c r="L18" t="n">
-        <v>3.8008</v>
+        <v>0.7729</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5198</v>
+        <v>-0.2472</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7775</v>
+        <v>-1.0838</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2578</v>
+        <v>0.8366</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6838</v>
+        <v>0.465</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8804</v>
+        <v>0.7551</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8035</v>
+        <v>-0.2902</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3558</v>
+        <v>-0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>2.428</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5298</v>
+        <v>-0.8164</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5648</v>
+        <v>3.1546</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.0946</v>
+        <v>-3.9709</v>
       </c>
       <c r="G19" t="n">
         <v>2.7458</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.827</v>
+        <v>-1.1136</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0376</v>
+        <v>-0.4479</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7894</v>
+        <v>-0.6657</v>
       </c>
       <c r="V19" t="n">
         <v>-2.6805</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>S. JOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6414</v>
+        <v>-1.8591</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1792</v>
+        <v>-2.0862</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4623</v>
+        <v>0.2271</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8907</v>
+        <v>-0.4078</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5894</v>
+        <v>-0.5149</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3012</v>
+        <v>0.1071</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4951</v>
+        <v>0.5004</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3479</v>
+        <v>0.39</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1472</v>
+        <v>0.1104</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6044</v>
+        <v>-0.9082</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7584</v>
+        <v>-0.9049</v>
       </c>
       <c r="O20" t="n">
-        <v>0.154</v>
+        <v>-0.0033</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3917</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.0775</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0395</v>
+        <v>-0.2671</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7134</v>
+        <v>0.1896</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4665</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. JOVIC</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9479</v>
+        <v>-2.6693</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.558</v>
+        <v>-1.2971</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3899</v>
+        <v>-1.3722</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4078</v>
+        <v>0.8907</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5149</v>
+        <v>0.5894</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1071</v>
+        <v>0.3012</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5004</v>
+        <v>1.4951</v>
       </c>
       <c r="K21" t="n">
-        <v>0.39</v>
+        <v>1.3479</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1104</v>
+        <v>0.1472</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9082</v>
+        <v>-0.6044</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9049</v>
+        <v>-0.7584</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0033</v>
+        <v>0.154</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6959</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1663</v>
+        <v>-0.7018</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7389</v>
+        <v>-0.0784</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4274</v>
+        <v>-0.6234</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.4665</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0377</v>
+        <v>-2.8132</v>
       </c>
       <c r="E22" t="n">
         <v>-2.0526</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9851</v>
+        <v>-0.7606000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9898</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7257</v>
+        <v>-0.5012</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.427</v>
+        <v>-0.2025</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3943</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1215</v>
+        <v>-5.4018</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3298</v>
+        <v>-1.5657</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.7917</v>
+        <v>-3.8361</v>
       </c>
       <c r="G23" t="n">
         <v>-0.992</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.217</v>
+        <v>-0.4973</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1142</v>
+        <v>-0.1217</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3312</v>
+        <v>-0.3756</v>
       </c>
       <c r="V23" t="n">
         <v>-3.2166</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.929499999999999</v>
+        <v>-4.356800000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5478000000000001</v>
+        <v>0.5479999999999996</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.4773</v>
+        <v>-4.9046</v>
       </c>
       <c r="G24" t="n">
-        <v>5.946199999999999</v>
+        <v>5.9462</v>
       </c>
       <c r="H24" t="n">
         <v>-5.8817</v>
@@ -2308,7 +2308,7 @@
         <v>9.5015</v>
       </c>
       <c r="M24" t="n">
-        <v>-6.098299999999999</v>
+        <v>-6.0983</v>
       </c>
       <c r="N24" t="n">
         <v>-8.4246</v>
@@ -2326,16 +2326,16 @@
         <v>15.077</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.225899999999999</v>
+        <v>-2.6533</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3121000000000005</v>
+        <v>-0.3121</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.9142</v>
+        <v>-2.3414</v>
       </c>
       <c r="V24" t="n">
-        <v>-5.3299</v>
+        <v>-5.329899999999999</v>
       </c>
       <c r="W24" t="n">
         <v>6.2118</v>
